--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T10:04:40+00:00</t>
+    <t>2026-08-28T05:37:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T05:37:53+00:00</t>
+    <t>2026-08-28T09:55:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:55:24+00:00</t>
+    <t>2026-08-28T09:59:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:59:46+00:00</t>
+    <t>2026-08-28T15:43:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:43:20+00:00</t>
+    <t>2026-08-31T15:04:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T15:04:35+00:00</t>
+    <t>2026-08-31T15:09:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
